--- a/Convert_from_xlsx_to_Json/table_normalization/economy-table103.xlsx
+++ b/Convert_from_xlsx_to_Json/table_normalization/economy-table103.xlsx
@@ -353,7 +353,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -369,12 +369,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF00B050"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -440,7 +434,7 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -506,26 +500,20 @@
     <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -550,6 +538,30 @@
         <name val="Arial"/>
         <scheme val="none"/>
       </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
       <numFmt numFmtId="164" formatCode="0.0"/>
       <fill>
         <patternFill patternType="none">
@@ -558,7 +570,7 @@
         </patternFill>
       </fill>
       <alignment horizontal="right" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
+      <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="medium">
           <color indexed="64"/>
         </left>
@@ -593,7 +605,7 @@
         </patternFill>
       </fill>
       <alignment horizontal="right" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
+      <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="medium">
           <color indexed="64"/>
         </left>
@@ -628,7 +640,7 @@
         </patternFill>
       </fill>
       <alignment horizontal="right" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
+      <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="medium">
           <color indexed="64"/>
         </left>
@@ -663,7 +675,7 @@
         </patternFill>
       </fill>
       <alignment horizontal="right" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
+      <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="medium">
           <color indexed="64"/>
         </left>
@@ -698,7 +710,7 @@
         </patternFill>
       </fill>
       <alignment horizontal="right" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
+      <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="medium">
           <color indexed="64"/>
         </left>
@@ -1058,6 +1070,13 @@
     </dxf>
     <dxf>
       <border outline="0">
+        <bottom style="medium">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
         <left style="medium">
           <color indexed="64"/>
         </left>
@@ -1067,37 +1086,6 @@
         <top style="medium">
           <color indexed="64"/>
         </top>
-        <bottom style="medium">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <border outline="0">
         <bottom style="medium">
           <color indexed="64"/>
         </bottom>
@@ -1153,7 +1141,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table15" displayName="Table15" ref="A6:O65" totalsRowShown="0" headerRowDxfId="18" dataDxfId="16" headerRowBorderDxfId="17" tableBorderDxfId="15">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table15" displayName="Table15" ref="A6:O65" totalsRowShown="0" headerRowDxfId="18" dataDxfId="0" headerRowBorderDxfId="16" tableBorderDxfId="17">
   <autoFilter ref="A6:O65">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -1172,21 +1160,21 @@
     <filterColumn colId="14" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="15">
-    <tableColumn id="1" name="Employment size, Country / English region, Industrial information / Sampling sector" dataDxfId="14"/>
-    <tableColumn id="2" name="Internal R&amp;D (percentage)" dataDxfId="13"/>
-    <tableColumn id="3" name="Acquisition of external R&amp;D (percentage)" dataDxfId="12"/>
-    <tableColumn id="4" name="Total machinery and equipment, computer hardware or software (percentage)" dataDxfId="11"/>
-    <tableColumn id="5" name="Machinery and equipment (percentage)" dataDxfId="10"/>
-    <tableColumn id="6" name="Computer hardware (percentage)" dataDxfId="9"/>
-    <tableColumn id="7" name="Computer software (percentage)" dataDxfId="8"/>
-    <tableColumn id="8" name="Acquisition of existing knowledge (percentage)" dataDxfId="7"/>
-    <tableColumn id="9" name="Training for innovative activities (percentage)" dataDxfId="6"/>
-    <tableColumn id="10" name="Any form of design activity (percentage)" dataDxfId="5"/>
-    <tableColumn id="11" name="Total market introduction of innovation including i) Changes to product or service design, ii) Market research, iii) Changes to marketing methods (percentage)" dataDxfId="4"/>
-    <tableColumn id="12" name="Changes to product or service design (percentage)" dataDxfId="3"/>
-    <tableColumn id="13" name="Market research (percentage)" dataDxfId="2"/>
-    <tableColumn id="14" name="Changes to marketing methods (percentage)" dataDxfId="1"/>
-    <tableColumn id="15" name="Launch advertising (percentage)" dataDxfId="0"/>
+    <tableColumn id="1" name="Employment size, Country / English region, Industrial information / Sampling sector" dataDxfId="15"/>
+    <tableColumn id="2" name="Internal R&amp;D (percentage)" dataDxfId="14"/>
+    <tableColumn id="3" name="Acquisition of external R&amp;D (percentage)" dataDxfId="13"/>
+    <tableColumn id="4" name="Total machinery and equipment, computer hardware or software (percentage)" dataDxfId="12"/>
+    <tableColumn id="5" name="Machinery and equipment (percentage)" dataDxfId="11"/>
+    <tableColumn id="6" name="Computer hardware (percentage)" dataDxfId="10"/>
+    <tableColumn id="7" name="Computer software (percentage)" dataDxfId="9"/>
+    <tableColumn id="8" name="Acquisition of existing knowledge (percentage)" dataDxfId="8"/>
+    <tableColumn id="9" name="Training for innovative activities (percentage)" dataDxfId="7"/>
+    <tableColumn id="10" name="Any form of design activity (percentage)" dataDxfId="6"/>
+    <tableColumn id="11" name="Total market introduction of innovation including i) Changes to product or service design, ii) Market research, iii) Changes to marketing methods (percentage)" dataDxfId="5"/>
+    <tableColumn id="12" name="Changes to product or service design (percentage)" dataDxfId="4"/>
+    <tableColumn id="13" name="Market research (percentage)" dataDxfId="3"/>
+    <tableColumn id="14" name="Changes to marketing methods (percentage)" dataDxfId="2"/>
+    <tableColumn id="15" name="Launch advertising (percentage)" dataDxfId="1"/>
   </tableColumns>
   <tableStyleInfo name="Table Style 1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1481,7 +1469,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1610,7 +1598,7 @@
       </c>
     </row>
     <row r="7" spans="1:15" ht="13">
-      <c r="A7" s="33" t="s">
+      <c r="A7" s="27" t="s">
         <v>18</v>
       </c>
       <c r="B7" s="8">
@@ -1657,23 +1645,23 @@
       </c>
     </row>
     <row r="8" spans="1:15" ht="20.75" customHeight="1">
-      <c r="A8" s="27" t="s">
+      <c r="A8" s="28" t="s">
         <v>19</v>
       </c>
-      <c r="B8" s="28"/>
-      <c r="C8" s="28"/>
-      <c r="D8" s="28"/>
-      <c r="E8" s="28"/>
-      <c r="F8" s="28"/>
-      <c r="G8" s="28"/>
-      <c r="H8" s="28"/>
-      <c r="I8" s="28"/>
-      <c r="J8" s="28"/>
-      <c r="K8" s="29"/>
-      <c r="L8" s="29"/>
-      <c r="M8" s="29"/>
-      <c r="N8" s="29"/>
-      <c r="O8" s="29"/>
+      <c r="B8" s="29"/>
+      <c r="C8" s="29"/>
+      <c r="D8" s="29"/>
+      <c r="E8" s="29"/>
+      <c r="F8" s="29"/>
+      <c r="G8" s="29"/>
+      <c r="H8" s="29"/>
+      <c r="I8" s="29"/>
+      <c r="J8" s="29"/>
+      <c r="K8" s="10"/>
+      <c r="L8" s="10"/>
+      <c r="M8" s="10"/>
+      <c r="N8" s="10"/>
+      <c r="O8" s="10"/>
     </row>
     <row r="9" spans="1:15">
       <c r="A9" s="11" t="s">
@@ -1914,20 +1902,20 @@
       <c r="A14" s="30" t="s">
         <v>25</v>
       </c>
-      <c r="B14" s="31"/>
-      <c r="C14" s="31"/>
-      <c r="D14" s="31"/>
-      <c r="E14" s="31"/>
-      <c r="F14" s="31"/>
-      <c r="G14" s="31"/>
-      <c r="H14" s="31"/>
-      <c r="I14" s="31"/>
-      <c r="J14" s="31"/>
-      <c r="K14" s="29"/>
-      <c r="L14" s="29"/>
-      <c r="M14" s="29"/>
-      <c r="N14" s="29"/>
-      <c r="O14" s="29"/>
+      <c r="B14" s="12"/>
+      <c r="C14" s="12"/>
+      <c r="D14" s="12"/>
+      <c r="E14" s="12"/>
+      <c r="F14" s="12"/>
+      <c r="G14" s="12"/>
+      <c r="H14" s="12"/>
+      <c r="I14" s="12"/>
+      <c r="J14" s="12"/>
+      <c r="K14" s="10"/>
+      <c r="L14" s="10"/>
+      <c r="M14" s="10"/>
+      <c r="N14" s="10"/>
+      <c r="O14" s="10"/>
     </row>
     <row r="15" spans="1:15">
       <c r="A15" s="11" t="s">
@@ -2118,23 +2106,23 @@
       </c>
     </row>
     <row r="19" spans="1:15" ht="20.75" customHeight="1">
-      <c r="A19" s="27" t="s">
+      <c r="A19" s="28" t="s">
         <v>30</v>
       </c>
-      <c r="B19" s="31"/>
-      <c r="C19" s="31"/>
-      <c r="D19" s="31"/>
-      <c r="E19" s="31"/>
-      <c r="F19" s="31"/>
-      <c r="G19" s="31"/>
-      <c r="H19" s="31"/>
-      <c r="I19" s="31"/>
-      <c r="J19" s="31"/>
-      <c r="K19" s="29"/>
-      <c r="L19" s="29"/>
-      <c r="M19" s="29"/>
-      <c r="N19" s="29"/>
-      <c r="O19" s="29"/>
+      <c r="B19" s="12"/>
+      <c r="C19" s="12"/>
+      <c r="D19" s="12"/>
+      <c r="E19" s="12"/>
+      <c r="F19" s="12"/>
+      <c r="G19" s="12"/>
+      <c r="H19" s="12"/>
+      <c r="I19" s="12"/>
+      <c r="J19" s="12"/>
+      <c r="K19" s="10"/>
+      <c r="L19" s="10"/>
+      <c r="M19" s="10"/>
+      <c r="N19" s="10"/>
+      <c r="O19" s="10"/>
     </row>
     <row r="20" spans="1:15">
       <c r="A20" s="11" t="s">
@@ -2560,23 +2548,23 @@
       </c>
     </row>
     <row r="29" spans="1:15" ht="20.75" customHeight="1">
-      <c r="A29" s="27" t="s">
+      <c r="A29" s="28" t="s">
         <v>40</v>
       </c>
-      <c r="B29" s="31"/>
-      <c r="C29" s="31"/>
-      <c r="D29" s="31"/>
-      <c r="E29" s="31"/>
-      <c r="F29" s="31"/>
-      <c r="G29" s="31"/>
-      <c r="H29" s="31"/>
-      <c r="I29" s="31"/>
-      <c r="J29" s="31"/>
-      <c r="K29" s="29"/>
-      <c r="L29" s="29"/>
-      <c r="M29" s="29"/>
-      <c r="N29" s="29"/>
-      <c r="O29" s="29"/>
+      <c r="B29" s="12"/>
+      <c r="C29" s="12"/>
+      <c r="D29" s="12"/>
+      <c r="E29" s="12"/>
+      <c r="F29" s="12"/>
+      <c r="G29" s="12"/>
+      <c r="H29" s="12"/>
+      <c r="I29" s="12"/>
+      <c r="J29" s="12"/>
+      <c r="K29" s="10"/>
+      <c r="L29" s="10"/>
+      <c r="M29" s="10"/>
+      <c r="N29" s="10"/>
+      <c r="O29" s="10"/>
     </row>
     <row r="30" spans="1:15">
       <c r="A30" s="11" t="s">
@@ -2908,23 +2896,23 @@
       </c>
     </row>
     <row r="37" spans="1:15" ht="30" customHeight="1">
-      <c r="A37" s="32" t="s">
+      <c r="A37" s="31" t="s">
         <v>49</v>
       </c>
-      <c r="B37" s="31"/>
-      <c r="C37" s="31"/>
-      <c r="D37" s="31"/>
-      <c r="E37" s="31"/>
-      <c r="F37" s="31"/>
-      <c r="G37" s="31"/>
-      <c r="H37" s="31"/>
-      <c r="I37" s="31"/>
-      <c r="J37" s="31"/>
-      <c r="K37" s="29"/>
-      <c r="L37" s="29"/>
-      <c r="M37" s="29"/>
-      <c r="N37" s="29"/>
-      <c r="O37" s="29"/>
+      <c r="B37" s="12"/>
+      <c r="C37" s="12"/>
+      <c r="D37" s="12"/>
+      <c r="E37" s="12"/>
+      <c r="F37" s="12"/>
+      <c r="G37" s="12"/>
+      <c r="H37" s="12"/>
+      <c r="I37" s="12"/>
+      <c r="J37" s="12"/>
+      <c r="K37" s="10"/>
+      <c r="L37" s="10"/>
+      <c r="M37" s="10"/>
+      <c r="N37" s="10"/>
+      <c r="O37" s="10"/>
     </row>
     <row r="38" spans="1:15">
       <c r="A38" s="13" t="s">
@@ -3024,20 +3012,20 @@
       <c r="A40" s="30" t="s">
         <v>52</v>
       </c>
-      <c r="B40" s="31"/>
-      <c r="C40" s="31"/>
-      <c r="D40" s="31"/>
-      <c r="E40" s="31"/>
-      <c r="F40" s="31"/>
-      <c r="G40" s="31"/>
-      <c r="H40" s="31"/>
-      <c r="I40" s="31"/>
-      <c r="J40" s="31"/>
-      <c r="K40" s="29"/>
-      <c r="L40" s="29"/>
-      <c r="M40" s="29"/>
-      <c r="N40" s="29"/>
-      <c r="O40" s="29"/>
+      <c r="B40" s="12"/>
+      <c r="C40" s="12"/>
+      <c r="D40" s="12"/>
+      <c r="E40" s="12"/>
+      <c r="F40" s="12"/>
+      <c r="G40" s="12"/>
+      <c r="H40" s="12"/>
+      <c r="I40" s="12"/>
+      <c r="J40" s="12"/>
+      <c r="K40" s="10"/>
+      <c r="L40" s="10"/>
+      <c r="M40" s="10"/>
+      <c r="N40" s="10"/>
+      <c r="O40" s="10"/>
     </row>
     <row r="41" spans="1:15">
       <c r="A41" s="11" t="s">
